--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="26.5546875" customWidth="1" min="3" max="3"/>
@@ -429,6 +429,7 @@
     <col width="12.109375" customWidth="1" min="9" max="9"/>
     <col width="14.5546875" customWidth="1" min="10" max="10"/>
     <col width="14.109375" customWidth="1" min="11" max="11"/>
+    <col width="14.109375" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,6 +526,11 @@
           <t>UseMaxValue</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>DomainRole</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -545,6 +551,11 @@
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>属性描述：定义和作用等</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Runtime v1 attribute domain role</t>
         </is>
       </c>
     </row>
@@ -584,6 +595,11 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>true</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -615,6 +631,11 @@
           <t>true</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="C7" s="2" t="n"/>
@@ -640,6 +661,11 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>true</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -670,6 +696,11 @@
           <t>true</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="n"/>
@@ -698,6 +729,11 @@
           <t>true</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="n"/>
@@ -726,6 +762,11 @@
           <t>true</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="n"/>
@@ -754,6 +795,11 @@
           <t>true</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="n"/>
@@ -782,6 +828,11 @@
           <t>true</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="n"/>
@@ -810,6 +861,11 @@
           <t>true</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="n">
@@ -846,6 +902,11 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>true</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -875,6 +936,11 @@
           <t>true</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
@@ -911,6 +977,11 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>true</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -939,11 +1010,43 @@
           <t>true</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>99999</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="n"/>
@@ -991,7 +1094,6 @@
     <row r="28">
       <c r="B28" s="2" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="B30" s="2" t="n"/>
     </row>
@@ -1000,8 +1102,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
